--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4696D96D-73FF-4373-A259-4ED789117245}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E941AF5-6545-43FC-B2C6-2BB38DCD2C4D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bit_Test_Single" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="query__4" localSheetId="1" hidden="1">Feuil1!$A$1:$E$23</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +39,16 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{8814D57D-DD73-4FA6-99DE-1F465DBA898F}" odcFile="C:\Users\jerom\Downloads\query (4).iqy" keepAlive="1" name="query (4)" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
+    <dbPr connection="Provider=Microsoft.Office.List.OLEDB.2.0;Data Source=&quot;&quot;;ApplicationName=Excel;Version=12.0.0.0" command="&lt;LIST&gt;&lt;VIEWGUID&gt;4B095B6C-E238-4145-AEAC-58FC81495ECD&lt;/VIEWGUID&gt;&lt;LISTNAME&gt;7043100c-5b9c-457f-ab38-a4bb8df4a390&lt;/LISTNAME&gt;&lt;LISTWEB&gt;https://groupefnac.sharepoint.com/sites/SAVVY_FNACDARTY/_vti_bin&lt;/LISTWEB&gt;&lt;LISTSUBWEB&gt;&lt;/LISTSUBWEB&gt;&lt;ROOTFOLDER&gt;/sites/SAVVY%5fFNACDARTY/Documents%20partages/DREAME%5fReferent/DREAME/Hub%5freferents%5fDreame/BIT%5fTest%5fSingle&lt;/ROOTFOLDER&gt;&lt;/LIST&gt;" commandType="5"/>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="93">
   <si>
     <t>Crash test</t>
   </si>
@@ -99,9 +111,6 @@
   </si>
   <si>
     <t>informations dictées</t>
-  </si>
-  <si>
-    <t>BIT-Test - crash test.MOV</t>
   </si>
   <si>
     <t>Vidéo</t>
@@ -146,19 +155,10 @@
 Test terminé</t>
   </si>
   <si>
-    <t>PSD Test.MOV</t>
-  </si>
-  <si>
     <t>TOF Test checking.PNG</t>
   </si>
   <si>
     <t>TOF Test checking passed.PNG</t>
-  </si>
-  <si>
-    <t>LDS test.MOV</t>
-  </si>
-  <si>
-    <t>Dust box test.MOV</t>
   </si>
   <si>
     <t>Test switch LDS</t>
@@ -189,12 +189,6 @@
   </si>
   <si>
     <t>Test gyroscope, rotation anti horaire puis horaire</t>
-  </si>
-  <si>
-    <t>Gyroscope.MOV</t>
-  </si>
-  <si>
-    <t>drive wheel test.MOV</t>
   </si>
   <si>
     <t>Test capteur bac à poussire</t>
@@ -257,39 +251,128 @@
     <t>Vérification de l'installation des serpillères</t>
   </si>
   <si>
-    <t>rag installation inspection.MOV</t>
-  </si>
-  <si>
-    <t>Wipe outside detection.MOV</t>
-  </si>
-  <si>
-    <t>wipe lifthing detection.mp4</t>
-  </si>
-  <si>
-    <t>side brush test.png</t>
-  </si>
-  <si>
     <t>Test réussi
 Test terminé</t>
   </si>
   <si>
-    <t>Roller test.MOV</t>
-  </si>
-  <si>
     <t>tank test.PNG</t>
   </si>
   <si>
     <t>fan test.png</t>
   </si>
   <si>
-    <t>fan test.MOV</t>
+    <t>https://vimeo.com/1204306133?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306060?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306102?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306126?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306061?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306062?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306127?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306125?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204306099?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Modifié</t>
+  </si>
+  <si>
+    <t>Modifié par</t>
+  </si>
+  <si>
+    <t>Type d'élément</t>
+  </si>
+  <si>
+    <t>Chemin d'accès</t>
+  </si>
+  <si>
+    <t>BIT_Test.pptx</t>
+  </si>
+  <si>
+    <t>LECONTE Jerome</t>
+  </si>
+  <si>
+    <t>Élément </t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/DREAME_Referent/DREAME/Hub_referents_Dreame/BIT_Test_Single</t>
+  </si>
+  <si>
+    <t>Forward Vision sensor test.PNG</t>
+  </si>
+  <si>
+    <t>Geomagnatic test confirm.png</t>
+  </si>
+  <si>
+    <t>Gyroscope test checking.PNG</t>
+  </si>
+  <si>
+    <t>IMG_7345.PNG</t>
+  </si>
+  <si>
+    <t>IMG_7346.PNG</t>
+  </si>
+  <si>
+    <t>IMG_7349.PNG</t>
+  </si>
+  <si>
+    <t>IMG_7350.PNG</t>
+  </si>
+  <si>
+    <t>IMG_7352.PNG</t>
+  </si>
+  <si>
+    <t>Menu Bit test.PNG</t>
+  </si>
+  <si>
+    <t>Menu BIT-Test.PNG</t>
+  </si>
+  <si>
+    <t>Placez le robot au sol, face inférieure orientée vers le bas.
+Après l’annonce vocale du robot, la brosse latérale effectue des rotations en marche avant puis en marche arrière à différentes vitesses. Une fois le test terminé, la brosse latérale s’arrête et le résultat du test est annoncé vocalement.</t>
+  </si>
+  <si>
+    <t>Lancez le test géomagnétique depuis l’interface BIT. Après l’annonce vocale du robot, celui-ci effectue un autocontrôle du capteur géomagnétique. À l’issue du test, le résultat est communiqué par message vocal.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Retirez le réservoir d’eau, puis remettez-le en place.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remarque : l’emplacement et la conception des réservoirs d’eau varient selon les modèles. Certains appareils sont équipés d’un réservoir intégré non amovible ; dans ce cas, il n’est pas nécessaire d’effectuer le test du réservoir d’eau. Veillez à identifier correctement le type de réservoir dont est équipé le modèle concerné.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,16 +394,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -328,11 +432,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -349,11 +467,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -364,6 +525,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query (4)" backgroundRefresh="0" connectionId="1" xr16:uid="{6E285143-0D50-4FB9-88A1-2137DB5E821D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="6">
+    <queryTableFields count="5">
+      <queryTableField id="5" name="Nom" tableColumnId="1"/>
+      <queryTableField id="1" name="Modifié" tableColumnId="2"/>
+      <queryTableField id="2" name="Modifié par" tableColumnId="3"/>
+      <queryTableField id="4" name="Type d'élément" tableColumnId="4"/>
+      <queryTableField id="3" name="Chemin d'accès" tableColumnId="5"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C2F6E42-8807-4FB8-AB0D-5A72D4B40973}" name="Tableau_query__4" displayName="Tableau_query__4" ref="A1:E23" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E23" xr:uid="{1C2F6E42-8807-4FB8-AB0D-5A72D4B40973}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{51192F08-EA34-4D7E-892C-5527C412EA39}" uniqueName="FileLeafRef" name="Nom" queryTableFieldId="5"/>
+    <tableColumn id="2" xr3:uid="{499A6632-CDE0-4BD2-B593-AA4B64AB3612}" uniqueName="Modified" name="Modifié" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1F43C3E3-99E6-4041-B2D2-B5F927C3842B}" uniqueName="Editor" name="Modifié par" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{81ED7A16-F42C-4FF6-9110-190249F8EE25}" uniqueName="FSObjType" name="Type d'élément" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{B8B7D7CA-5B22-43FF-A8A4-EFF15C1B7C6E}" uniqueName="FileDirRef" name="Chemin d'accès" queryTableFieldId="3" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,9 +824,9 @@
     <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -652,14 +841,14 @@
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
+      <c r="F2" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>19</v>
@@ -674,37 +863,40 @@
         <v>Test de collision</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="str">
-        <f t="shared" ref="B4:B19" si="0">_xlfn.TRANSLATE(A4,"en","fr")</f>
+        <f t="shared" ref="B4:B17" si="0">_xlfn.TRANSLATE(A4,"en","fr")</f>
         <v>Test du capteur vers le bas</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -713,16 +905,17 @@
         <v>Test du capteur de vision avant</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
@@ -734,13 +927,15 @@
         <v>Test PSD/ Power Spectral Density</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
@@ -752,16 +947,17 @@
         <v>Test TOF / Time Of Flight</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="D7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
@@ -773,40 +969,42 @@
         <v>Test LDS / Laser Distance Sensor</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test des roues motrices</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -815,19 +1013,19 @@
         <v>Test du gyroscope</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
@@ -839,11 +1037,18 @@
         <v>Test géomagnatique</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -852,32 +1057,39 @@
         <v>Test de la boîte à poussière</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -886,15 +1098,16 @@
         <v>Test du ventilateur</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>73</v>
+      <c r="D14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -903,29 +1116,35 @@
         <v>Test de brossage latéral</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="3"/>
+      <c r="D15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -934,8 +1153,10 @@
         <v>Détection de levage par nettoyage</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="G17" s="3"/>
     </row>
@@ -944,13 +1165,15 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="G18" s="3"/>
     </row>
@@ -959,20 +1182,463 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F12" r:id="rId1" xr:uid="{8311304E-41FB-4B2E-9AED-F49284910EBC}"/>
+    <hyperlink ref="F14" r:id="rId2" xr:uid="{55486497-4BF6-4670-804B-2D86E364272C}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{ACE053D1-986B-4C7F-9641-AABBB418751D}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{BFF3F5E7-CD3D-4B80-9333-C34DC2A40B3D}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{D34255A3-E814-400B-83C5-A061BA7CC94F}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{6AF01FE5-6CCD-4E38-9DB1-6F84BFAD0FCA}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{C905FA5E-63A7-4F15-B078-AA4EA3FE5A2B}"/>
+    <hyperlink ref="F3" r:id="rId8" xr:uid="{B3A9FC41-7B54-4E77-9541-78B8B410AFAB}"/>
+    <hyperlink ref="F18" r:id="rId9" xr:uid="{E4CFEE98-FD6D-46F5-9D7C-3F98A9566C0E}"/>
+    <hyperlink ref="F17" r:id="rId10" xr:uid="{577E6ACD-1D22-4E26-8D86-A53AFBF0D395}"/>
+    <hyperlink ref="F19" r:id="rId11" xr:uid="{6DDD865A-EB98-493F-A02E-2CE9D5CEA685}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AC455B-BEFC-42EF-97B5-31D9853CFD3B}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="52.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46197.897337962961</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="8">
+        <v>46197.897037037037</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46197.897037037037</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46197.897048611114</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8">
+        <v>46197.897048611114</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="8">
+        <v>46197.897048611114</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="8">
+        <v>46197.897048611114</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8">
+        <v>46197.897048611114</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="8">
+        <v>46197.897060185183</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46197.89707175926</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="8">
+        <v>46197.89707175926</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46197.89707175926</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="8">
+        <v>46197.89707175926</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46197.897037037037</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="8">
+        <v>46197.897037037037</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46197.897037037037</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{42440853-24CC-44FD-8BE2-819E7C00100C}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{4A124001-B106-4905-8785-E6F18DF65F4E}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{C4107B62-487C-4760-BB0E-0333B999DDA1}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{07B9E09A-BBDF-4642-9D44-C4625DAA02C5}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{69D1447D-E1D2-4096-92F8-005086955F94}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{C0A54B29-40C8-47D4-9383-6C2AC8CA1536}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{F396C26E-91B4-40BF-B5A2-2DFB7490BFDF}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{E7E44BE2-C4C3-4FE8-9B90-617A42E373F6}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{2963E887-6BC4-44D0-BAFF-6B037543138E}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{48104FDF-0756-4759-900B-F2FFE3EE5FD6}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{BA32ED21-4A32-4CCF-833A-BF0788EEE3D3}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{D4F6AD53-5E3E-4448-89CF-C3C48DB8D926}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{68935788-2EDA-4591-AD75-A3F7CA8A67C7}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{7FCCB3E6-E9E1-4F7C-880F-87CA6529FF70}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{276FEB22-7439-4963-B393-59FF77D03C7E}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{4A9D4F4E-04C0-408D-B2EC-B2734FAA6B85}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{E8645537-2DB1-4B02-8FD0-E286AA79849E}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{1B2DECC8-CD48-42A6-8ABD-00963BD8E327}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{61AAF7A8-51A9-4EC3-89F7-F467F303B7FF}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{6C53F7A0-F920-495E-B394-0EA19914148C}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{1D2A369A-14ED-4F53-8667-3700C394FA6E}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{ABCA4607-BA22-4D16-A810-F84C4E4FD3B3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId23"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E941AF5-6545-43FC-B2C6-2BB38DCD2C4D}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF4A11FD-38E2-409C-8528-F419EC5DF908}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bit_Test_Single" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="94">
   <si>
     <t>Crash test</t>
   </si>
@@ -366,6 +366,9 @@
       </rPr>
       <t>Remarque : l’emplacement et la conception des réservoirs d’eau varient selon les modèles. Certains appareils sont équipés d’un réservoir intégré non amovible ; dans ce cas, il n’est pas nécessaire d’effectuer le test du réservoir d’eau. Veillez à identifier correctement le type de réservoir dont est équipé le modèle concerné.</t>
     </r>
+  </si>
+  <si>
+    <t>Test capteurs de chute</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -476,19 +479,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -824,8 +821,8 @@
     <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -841,10 +838,10 @@
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -865,10 +862,10 @@
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="11"/>
+      <c r="D3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="6" t="s">
         <v>68</v>
       </c>
@@ -880,17 +877,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="str">
-        <f t="shared" ref="B4:B17" si="0">_xlfn.TRANSLATE(A4,"en","fr")</f>
-        <v>Test du capteur vers le bas</v>
+      <c r="B4" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="11"/>
+      <c r="D4" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
         <v>29</v>
@@ -901,16 +897,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B4:B17" si="0">_xlfn.TRANSLATE(A5,"en","fr")</f>
         <v>Test du capteur de vision avant</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="3"/>
@@ -929,8 +925,8 @@
       <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
         <v>67</v>
       </c>
@@ -949,10 +945,10 @@
       <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="D7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F7" s="3"/>
@@ -971,8 +967,8 @@
       <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="6" t="s">
         <v>67</v>
       </c>
@@ -991,10 +987,10 @@
       <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1015,10 +1011,10 @@
       <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -1039,10 +1035,10 @@
       <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="11"/>
+      <c r="D11" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
         <v>91</v>
@@ -1059,10 +1055,10 @@
       <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="11"/>
+      <c r="D12" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="6" t="s">
         <v>62</v>
       </c>
@@ -1078,10 +1074,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="16" t="s">
+      <c r="D13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F13" s="3"/>
@@ -1098,10 +1094,10 @@
         <v>Test du ventilateur</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="11"/>
+      <c r="D14" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="6" t="s">
         <v>63</v>
       </c>
@@ -1119,7 +1115,7 @@
       <c r="D15" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
         <v>90</v>
@@ -1135,8 +1131,8 @@
       <c r="C16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
       <c r="F16" s="6" t="s">
         <v>64</v>
       </c>
@@ -1153,8 +1149,8 @@
         <v>Détection de levage par nettoyage</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
       <c r="F17" s="6" t="s">
         <v>69</v>
       </c>
@@ -1170,8 +1166,8 @@
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
       <c r="F18" s="6" t="s">
         <v>69</v>
       </c>
@@ -1187,8 +1183,8 @@
       <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
       <c r="F19" s="6" t="s">
         <v>70</v>
       </c>

--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF4A11FD-38E2-409C-8528-F419EC5DF908}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7540BE-C52E-4990-9EF8-48B1093C8B8C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bit_Test_Single" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
   <si>
     <t>Crash test</t>
   </si>
@@ -370,12 +370,18 @@
   <si>
     <t>Test capteurs de chute</t>
   </si>
+  <si>
+    <t>tank test 2.PNG</t>
+  </si>
+  <si>
+    <t>side brush test.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,19 +418,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -453,7 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -476,9 +481,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -488,9 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -816,18 +816,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="4" customFormat="1">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -838,10 +838,10 @@
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -851,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="86.4">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -862,8 +862,8 @@
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>79</v>
+      <c r="D3" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="6" t="s">
@@ -873,7 +873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -883,8 +883,8 @@
       <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>79</v>
+      <c r="D4" t="s">
+        <v>24</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -892,29 +892,29 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="str">
-        <f t="shared" ref="B4:B17" si="0">_xlfn.TRANSLATE(A5,"en","fr")</f>
+        <f t="shared" ref="B5:B17" si="0">_xlfn.TRANSLATE(A5,"en","fr")</f>
         <v>Test du capteur de vision avant</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>79</v>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="86.4">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -934,7 +934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="2" customFormat="1" ht="129.6">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -945,18 +945,18 @@
       <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>79</v>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="72">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -976,7 +976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -987,11 +987,11 @@
       <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>79</v>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>65</v>
@@ -1000,7 +1000,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -1011,11 +1011,11 @@
       <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>79</v>
+      <c r="D10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>66</v>
@@ -1024,7 +1024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="115.2">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1035,16 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>79</v>
-      </c>
+      <c r="D11" s="11"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="57.6">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1055,8 +1053,8 @@
       <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>79</v>
+      <c r="D12" t="s">
+        <v>45</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="6" t="s">
@@ -1066,7 +1064,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="115.2">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1074,18 +1072,18 @@
         <v>47</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>79</v>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1094,8 +1092,8 @@
         <v>Test du ventilateur</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="12" t="s">
-        <v>79</v>
+      <c r="D14" t="s">
+        <v>61</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="6" t="s">
@@ -1103,7 +1101,7 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="100.8">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1112,8 +1110,8 @@
         <v>Test de brossage latéral</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="10" t="s">
-        <v>79</v>
+      <c r="D15" t="s">
+        <v>95</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1121,7 +1119,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="100.8">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -1140,7 +1138,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -1156,7 +1154,7 @@
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="43.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1173,7 +1171,7 @@
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="57.6">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -1214,9 +1212,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AC455B-BEFC-42EF-97B5-31D9853CFD3B}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="52.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="52.88671875" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>71</v>
       </c>
@@ -1233,7 +1231,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
         <v>76</v>
       </c>
@@ -1250,7 +1248,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
         <v>26</v>
       </c>
@@ -1267,7 +1265,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1284,7 +1282,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
@@ -1301,7 +1299,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
         <v>41</v>
       </c>
@@ -1318,7 +1316,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>45</v>
       </c>
@@ -1335,7 +1333,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
         <v>61</v>
       </c>
@@ -1352,7 +1350,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
         <v>80</v>
       </c>
@@ -1369,7 +1367,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
@@ -1386,7 +1384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
         <v>81</v>
       </c>
@@ -1403,7 +1401,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1420,7 +1418,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
         <v>82</v>
       </c>
@@ -1437,7 +1435,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
         <v>83</v>
       </c>
@@ -1454,7 +1452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="7" t="s">
         <v>84</v>
       </c>
@@ -1471,7 +1469,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
         <v>85</v>
       </c>
@@ -1488,7 +1486,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
         <v>86</v>
       </c>
@@ -1505,7 +1503,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
         <v>87</v>
       </c>
@@ -1522,7 +1520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
         <v>88</v>
       </c>
@@ -1539,7 +1537,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
         <v>89</v>
       </c>
@@ -1556,7 +1554,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
         <v>60</v>
       </c>
@@ -1573,7 +1571,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
         <v>34</v>
       </c>
@@ -1590,7 +1588,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
         <v>33</v>
       </c>

--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7540BE-C52E-4990-9EF8-48B1093C8B8C}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14D5E3FF-0F03-4E47-9F98-68FA952F3A53}"/>
   <bookViews>
-    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bit_Test_Single" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="101">
   <si>
     <t>Crash test</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>Test du module vision</t>
-  </si>
-  <si>
-    <t>Test capteur de vide</t>
   </si>
   <si>
     <t>Forward Vision sensor test Test checking….</t>
@@ -280,12 +277,6 @@
   </si>
   <si>
     <t>https://vimeo.com/1204306127?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1204306125?share=copy&amp;fl=sv&amp;fe=ci</t>
-  </si>
-  <si>
-    <t>https://vimeo.com/1204306099?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
   <si>
     <t>Nom</t>
@@ -376,12 +367,138 @@
   <si>
     <t>side brush test.png</t>
   </si>
+  <si>
+    <t>Accès au mode BIT Test Dreame/Mova</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le mode </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>BIT Test (Built-In Test)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> permet de vérifier individuellement les principaux composants du robot Dreame et MOVA afin de confirmer un diagnostic ou valider une réparation après intervention.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Prérequis
+Avant d'accéder au mode BIT, les conditions suivantes doivent être réunies :
+L'application Dreamehome ou MovaHome doit être installée sur un smartphone connecté au robot.
+Le compte utilisé doit disposer des droits Whitelist de calibrage.
+Pour faire une demande d'accès au mode maintenance faite une demande en cliquant ici "https://fnacdarty.mayday.fr/desk/parametric/default/contents/69d7596991a65edbd2007f35"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Le robot doit être mis à jour avec la dernière version du firmware disponible.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Test capteur de vide / chute
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remarque :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Attention de bien prendre le robot sur l'avant et l'arrière, les capteurs de chute se trouvent sur les cotés droites et gauche</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Procédure d'accès depuis l'application
+Ouvrir l'application MovaHome ou Dreamehome et se connecter au robot.
+Appuyer sur les trois points situés en haut à droite de l'écran pour accéder aux paramètres.
+Ouvrir le menu Cleaning History (Historique de nettoyage).
+Cliquer 10 fois rapidement sur la zone affichant les statistiques du robot (Total Time / Total Area / Total Times).
+L'écran Network Info apparaît.
+Sélectionner BIT Check.
+L'écran BIT s'ouvre et donne accès à l'ensemble des tests unitaires disponibles.
+Mode BIT séquentiel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(sans application)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Il est également possible d'exécuter un contrôle complet directement depuis le robot :
+Allumer le robot.
+Dans les 3 minutes suivant la mise sous tension, maintenir le bouton Recharge enfoncé.
+Appuyer 5 fois sur le bouton Power.
+Le robot entre alors dans le mode BIT séquentiel, qui exécute automatiquement une série de tests sur les différents composants.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204328154?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204328155?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204328156?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +540,36 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -458,7 +605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -491,6 +638,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -815,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G19"/>
+  <dimension ref="A2:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
@@ -851,359 +1007,379 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="86.4">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="388.8">
+      <c r="A3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="86.4">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="str">
-        <f>_xlfn.TRANSLATE(A3,"en","fr")</f>
+      <c r="B4" s="3" t="str">
+        <f>_xlfn.TRANSLATE(A4,"en","fr")</f>
         <v>Test de collision</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="57.6">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <f t="shared" ref="B5:B17" si="0">_xlfn.TRANSLATE(A5,"en","fr")</f>
-        <v>Test du capteur de vision avant</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="28.8">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f t="shared" ref="B6:B18" si="0">_xlfn.TRANSLATE(A6,"en","fr")</f>
+        <v>Test du capteur de vision avant</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" ht="86.4">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:7" s="2" customFormat="1" ht="86.4">
+      <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="str">
-        <f>_xlfn.TRANSLATE(A6,"en","fr") &amp; "/ Power Spectral Density"</f>
+      <c r="B7" s="3" t="str">
+        <f>_xlfn.TRANSLATE(A7,"en","fr") &amp; "/ Power Spectral Density"</f>
         <v>Test PSD/ Power Spectral Density</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="129.6">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>_xlfn.TRANSLATE(A8,"en","fr") &amp; " / Time Of Flight"</f>
+        <v>Test TOF / Time Of Flight</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" ht="129.6">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <f>_xlfn.TRANSLATE(A7,"en","fr") &amp; " / Time Of Flight"</f>
-        <v>Test TOF / Time Of Flight</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="72">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f>_xlfn.TRANSLATE(A9,"en","fr") &amp; " / Laser Distance Sensor"</f>
+        <v>Test LDS / Laser Distance Sensor</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="28.8">
+      <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" ht="72">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="str">
-        <f>_xlfn.TRANSLATE(A8,"en","fr") &amp; " / Laser Distance Sensor"</f>
-        <v>Test LDS / Laser Distance Sensor</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="3" t="str">
+      <c r="B10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test des roues motrices</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A10" s="2" t="s">
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="28.8">
+      <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test du gyroscope</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="115.2">
-      <c r="A11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="115.2">
+      <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test géomagnatique</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="57.6">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="57.6">
+      <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="str">
+      <c r="B13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test de la boîte à poussière</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="115.2">
+      <c r="A14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="115.2">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="28.8">
+      <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test du ventilateur</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="100.8">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="100.8">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Test de brossage latéral</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="100.8">
-      <c r="A16" s="2" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="100.8">
+      <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="28.8">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Détection de levage par nettoyage</v>
-      </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="43.2">
+        <v>63</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Détection de levage par nettoyage</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="57.6">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="43.2">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="57.6">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>56</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1" xr:uid="{8311304E-41FB-4B2E-9AED-F49284910EBC}"/>
-    <hyperlink ref="F14" r:id="rId2" xr:uid="{55486497-4BF6-4670-804B-2D86E364272C}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{ACE053D1-986B-4C7F-9641-AABBB418751D}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{BFF3F5E7-CD3D-4B80-9333-C34DC2A40B3D}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{D34255A3-E814-400B-83C5-A061BA7CC94F}"/>
-    <hyperlink ref="F8" r:id="rId6" xr:uid="{6AF01FE5-6CCD-4E38-9DB1-6F84BFAD0FCA}"/>
-    <hyperlink ref="F6" r:id="rId7" xr:uid="{C905FA5E-63A7-4F15-B078-AA4EA3FE5A2B}"/>
-    <hyperlink ref="F3" r:id="rId8" xr:uid="{B3A9FC41-7B54-4E77-9541-78B8B410AFAB}"/>
-    <hyperlink ref="F18" r:id="rId9" xr:uid="{E4CFEE98-FD6D-46F5-9D7C-3F98A9566C0E}"/>
-    <hyperlink ref="F17" r:id="rId10" xr:uid="{577E6ACD-1D22-4E26-8D86-A53AFBF0D395}"/>
-    <hyperlink ref="F19" r:id="rId11" xr:uid="{6DDD865A-EB98-493F-A02E-2CE9D5CEA685}"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{8311304E-41FB-4B2E-9AED-F49284910EBC}"/>
+    <hyperlink ref="F15" r:id="rId2" xr:uid="{55486497-4BF6-4670-804B-2D86E364272C}"/>
+    <hyperlink ref="F17" r:id="rId3" xr:uid="{ACE053D1-986B-4C7F-9641-AABBB418751D}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{BFF3F5E7-CD3D-4B80-9333-C34DC2A40B3D}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{D34255A3-E814-400B-83C5-A061BA7CC94F}"/>
+    <hyperlink ref="F9" r:id="rId6" xr:uid="{6AF01FE5-6CCD-4E38-9DB1-6F84BFAD0FCA}"/>
+    <hyperlink ref="F7" r:id="rId7" xr:uid="{C905FA5E-63A7-4F15-B078-AA4EA3FE5A2B}"/>
+    <hyperlink ref="F4" r:id="rId8" xr:uid="{B3A9FC41-7B54-4E77-9541-78B8B410AFAB}"/>
+    <hyperlink ref="F18" r:id="rId9" xr:uid="{2A0D0948-03DF-4066-8EAF-7160F12558D1}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{C970B4A4-349B-4FD3-832E-A4BF7F1AA092}"/>
+    <hyperlink ref="F19" r:id="rId11" xr:uid="{6E28CCC8-3EA7-40DD-8819-91257F796320}"/>
+    <hyperlink ref="F3" r:id="rId12" xr:uid="{10329BCE-4F0B-477D-88B4-A1079250A19C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1216,36 +1392,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>72</v>
-      </c>
-      <c r="C1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B2" s="8">
         <v>46197.897337962961</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1256,13 +1432,13 @@
         <v>46197.897037037037</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1273,98 +1449,98 @@
         <v>46197.897037037037</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="8">
         <v>46197.897048611114</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8">
         <v>46197.897048611114</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="8">
         <v>46197.897048611114</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B9" s="8">
         <v>46197.897048611114</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1375,234 +1551,234 @@
         <v>46197.897048611114</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B13" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B14" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B15" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B16" s="8">
         <v>46197.897060185183</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B17" s="8">
         <v>46197.89707175926</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B18" s="8">
         <v>46197.89707175926</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B19" s="8">
         <v>46197.89707175926</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B20" s="8">
         <v>46197.89707175926</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="8">
         <v>46197.897037037037</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="8">
         <v>46197.897037037037</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="8">
         <v>46197.897037037037</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14D5E3FF-0F03-4E47-9F98-68FA952F3A53}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B9EDD6-6B11-45AA-9F59-3C2834E1B6F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="102">
   <si>
     <t>Crash test</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>https://vimeo.com/1204328156?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/1204328262?share=copy&amp;fl=sv&amp;fe=ci</t>
   </si>
 </sst>
 </file>
@@ -645,7 +648,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1020,7 +1023,7 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>97</v>
@@ -1379,7 +1382,7 @@
     <hyperlink ref="F18" r:id="rId9" xr:uid="{2A0D0948-03DF-4066-8EAF-7160F12558D1}"/>
     <hyperlink ref="F20" r:id="rId10" xr:uid="{C970B4A4-349B-4FD3-832E-A4BF7F1AA092}"/>
     <hyperlink ref="F19" r:id="rId11" xr:uid="{6E28CCC8-3EA7-40DD-8819-91257F796320}"/>
-    <hyperlink ref="F3" r:id="rId12" xr:uid="{10329BCE-4F0B-477D-88B4-A1079250A19C}"/>
+    <hyperlink ref="F3" r:id="rId12" xr:uid="{1E3873C9-1BB3-4E4B-B01C-8DC049280A8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B9EDD6-6B11-45AA-9F59-3C2834E1B6F9}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE3A614-E5F5-4ABD-8D0E-E02E18B05574}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,27 +396,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Prérequis
-Avant d'accéder au mode BIT, les conditions suivantes doivent être réunies :
-L'application Dreamehome ou MovaHome doit être installée sur un smartphone connecté au robot.
-Le compte utilisé doit disposer des droits Whitelist de calibrage.
-Pour faire une demande d'accès au mode maintenance faite une demande en cliquant ici "https://fnacdarty.mayday.fr/desk/parametric/default/contents/69d7596991a65edbd2007f35"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Le robot doit être mis à jour avec la dernière version du firmware disponible.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Test capteur de vide / chute
 </t>
     </r>
@@ -495,6 +474,27 @@
   </si>
   <si>
     <t>https://vimeo.com/1204328262?share=copy&amp;fl=sv&amp;fe=ci</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Prérequis
+Avant d'accéder au mode BIT, les conditions suivantes doivent être réunies :
+L'application Dreamehome ou MovaHome doit être installée sur un smartphone connecté au robot.
+Le compte utilisé doit disposer des droits Whitelist de calibrage.
+Pour faire une demande d'accès au mode maintenance faite une demande en cliquantsur le lien ci dessous
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Le robot doit être mis à jour avec la dernière version du firmware disponible.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -642,12 +642,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1011,22 +1014,25 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" ht="388.8">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="10"/>
+      <c r="C3" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="15" t="str">
+        <f>HYPERLINK("https://fnacdarty.mayday.fr/desk/parametric/default/contents/69d7596991a65edbd2007f35","Cliquer ici pour effectuer une demande d'accès au BIT Test via l'application")</f>
+        <v>Cliquer ici pour effectuer une demande d'accès au BIT Test via l'application</v>
+      </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="16" t="s">
-        <v>101</v>
+      <c r="F3" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="86.4">
@@ -1034,8 +1040,8 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="str">
-        <f>_xlfn.TRANSLATE(A4,"en","fr")</f>
-        <v>Test de collision</v>
+        <f>_xlfn.TRANSLATE(A4,"en","fr") &amp; " / Bumper"</f>
+        <v>Test de collision / Bumper</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -1067,7 +1073,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="28.8">
@@ -1328,7 +1334,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3"/>
     </row>
@@ -1345,7 +1351,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="3"/>
     </row>
@@ -1362,7 +1368,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>55</v>

--- a/images/procedure-acces/BIT-test/BIT-Test.xlsx
+++ b/images/procedure-acces/BIT-test/BIT-Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/hub_dreame_mova/images/BIT-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE3A614-E5F5-4ABD-8D0E-E02E18B05574}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="11_AD4D9D64A577C15A4A54181B381C6B805BDEDD8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D49915FC-11D8-4825-8064-6F7A5204560F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bit_Test_Single" sheetId="1" r:id="rId1"/>
@@ -362,9 +362,6 @@
     <t>Test capteurs de chute</t>
   </si>
   <si>
-    <t>tank test 2.PNG</t>
-  </si>
-  <si>
     <t>side brush test.png</t>
   </si>
   <si>
@@ -495,6 +492,9 @@
       </rPr>
       <t>Le robot doit être mis à jour avec la dernière version du firmware disponible.</t>
     </r>
+  </si>
+  <si>
+    <t>Tank test 2.png</t>
   </si>
 </sst>
 </file>
@@ -1015,13 +1015,13 @@
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" ht="388.8">
       <c r="A3" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="C3" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="15" t="str">
         <f>HYPERLINK("https://fnacdarty.mayday.fr/desk/parametric/default/contents/69d7596991a65edbd2007f35","Cliquer ici pour effectuer une demande d'accès au BIT Test via l'application")</f>
@@ -1029,10 +1029,10 @@
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="86.4">
@@ -1073,7 +1073,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="28.8">
@@ -1259,8 +1259,8 @@
       <c r="D14" t="s">
         <v>59</v>
       </c>
-      <c r="E14" t="s">
-        <v>91</v>
+      <c r="E14" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,7 +1334,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3"/>
     </row>
@@ -1351,7 +1351,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3"/>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>55</v>
@@ -1389,6 +1389,7 @@
     <hyperlink ref="F20" r:id="rId10" xr:uid="{C970B4A4-349B-4FD3-832E-A4BF7F1AA092}"/>
     <hyperlink ref="F19" r:id="rId11" xr:uid="{6E28CCC8-3EA7-40DD-8819-91257F796320}"/>
     <hyperlink ref="F3" r:id="rId12" xr:uid="{1E3873C9-1BB3-4E4B-B01C-8DC049280A8C}"/>
+    <hyperlink ref="E14" r:id="rId13" tooltip="Tank test 2.png" display="https://github.com/savvyfnacdarty/dreame-search-sav/blob/main/images/procedure-acces/BIT-test/Tank test 2.png" xr:uid="{D2E70C29-FE06-47D7-972C-AB3BC66FFC26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
